--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Поплаухина- бухгалтер/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Поплаухина- бухгалтер/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92574945951</v>
+        <v>46157.93119080596</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Поплаухина- бухгалтер/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Поплаухина- бухгалтер/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93119080596</v>
+        <v>46157.9318433176</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Поплаухина- бухгалтер/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Поплаухина- бухгалтер/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.9318433176</v>
+        <v>46157.93406312925</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Поплаухина- бухгалтер/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Поплаухина- бухгалтер/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93406312925</v>
+        <v>46157.93724323384</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Поплаухина- бухгалтер/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Поплаухина- бухгалтер/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93724323384</v>
+        <v>46158.28222065506</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Поплаухина- бухгалтер/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Поплаухина- бухгалтер/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28222065506</v>
+        <v>46158.29703349705</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Поплаухина- бухгалтер/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Поплаухина- бухгалтер/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29703349705</v>
+        <v>46158.29821913462</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Поплаухина- бухгалтер/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Поплаухина- бухгалтер/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29821913462</v>
+        <v>46158.3339302444</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Поплаухина- бухгалтер/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Поплаухина- бухгалтер/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.3339302444</v>
+        <v>46158.36862805953</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Поплаухина- бухгалтер/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Поплаухина- бухгалтер/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36862805953</v>
+        <v>46158.37293778927</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
